--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:29:54+00:00</t>
+          <t>2026-05-10T00:27:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:27:13+00:00</t>
+          <t>2026-05-11T00:27:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:41+00:00</t>
+          <t>2026-05-12T00:28:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:28:11+00:00</t>
+          <t>2026-05-13T00:30:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:30:44+00:00</t>
+          <t>2026-05-14T00:31:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:31:42+00:00</t>
+          <t>2026-05-15T00:29:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:29:18+00:00</t>
+          <t>2026-05-16T00:27:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:57+00:00</t>
+          <t>2026-05-17T00:28:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:49+00:00</t>
+          <t>2026-05-18T00:29:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:23+00:00</t>
+          <t>2026-05-19T00:32:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:49+00:00</t>
+          <t>2026-05-20T00:34:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:34:24+00:00</t>
+          <t>2026-05-21T00:35:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21T00:35:12+00:00</t>
+          <t>2026-05-22T00:32:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:32:33+00:00</t>
+          <t>2026-05-23T00:33:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:33:26+00:00</t>
+          <t>2026-05-24T00:31:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:31:58+00:00</t>
+          <t>2026-05-25T00:34:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:34:18+00:00</t>
+          <t>2026-05-26T00:34:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:34:03+00:00</t>
+          <t>2026-05-27T00:33:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:58+00:00</t>
+          <t>2026-05-28T00:30:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:30:29+00:00</t>
+          <t>2026-05-29T00:36:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:36:36+00:00</t>
+          <t>2026-05-30T00:33:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:33:04+00:00</t>
+          <t>2026-05-31T00:34:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:34:19+00:00</t>
+          <t>2026-06-01T00:36:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:36:55+00:00</t>
+          <t>2026-06-02T00:40:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:40:41+00:00</t>
+          <t>2026-06-03T00:45:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:45:43+00:00</t>
+          <t>2026-06-04T00:43:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:40+00:00</t>
+          <t>2026-06-05T00:36:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:53+00:00</t>
+          <t>2026-06-06T00:34:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:52+00:00</t>
+          <t>2026-06-07T00:35:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:54+00:00</t>
+          <t>2026-06-08T00:37:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:37:24+00:00</t>
+          <t>2026-06-09T00:32:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:32:33+00:00</t>
+          <t>2026-06-10T00:38:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:38:32+00:00</t>
+          <t>2026-06-11T00:42:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:42:44+00:00</t>
+          <t>2026-06-12T00:48:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:48:14+00:00</t>
+          <t>2026-06-13T00:39:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:39:30+00:00</t>
+          <t>2026-06-14T00:38:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:38:17+00:00</t>
+          <t>2026-06-15T00:39:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:39:31+00:00</t>
+          <t>2026-06-16T00:50:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:50:07+00:00</t>
+          <t>2026-06-17T00:40:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:40:07+00:00</t>
+          <t>2026-06-18T00:44:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:44:10+00:00</t>
+          <t>2026-06-19T00:44:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:44:10+00:00</t>
+          <t>2026-06-20T00:36:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:36:21+00:00</t>
+          <t>2026-06-21T00:39:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:39:24+00:00</t>
+          <t>2026-06-22T00:38:25+00:00</t>
         </is>
       </c>
     </row>
